--- a/data/quotas/quota_2026_소프트웨어_사업자_조사쿼터_1791810359821.xlsx
+++ b/data/quotas/quota_2026_소프트웨어_사업자_조사쿼터_1791810359821.xlsx
@@ -397,14 +397,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:H3"/>
   <cols>
     <col min="1" max="1" width="10.83203125" customWidth="1"/>
     <col min="2" max="2" width="38.83203125" customWidth="1"/>
     <col min="3" max="3" width="19.234375" customWidth="1"/>
     <col min="4" max="4" width="14.83203125" customWidth="1"/>
-    <col min="5" max="5" width="14.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.83203125" customWidth="1"/>
+    <col min="6" max="6" width="10.83203125" customWidth="1"/>
+    <col min="7" max="7" width="14.83203125" customWidth="1"/>
+    <col min="8" max="8" width="35.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -421,9 +423,15 @@
         <v>대표자이름</v>
       </c>
       <c r="E1" t="str">
+        <v>성별</v>
+      </c>
+      <c r="F1" t="str">
+        <v>나이</v>
+      </c>
+      <c r="G1" t="str">
         <v>전화번호</v>
       </c>
-      <c r="F1" t="str">
+      <c r="H1" t="str">
         <v>사업장주소</v>
       </c>
     </row>
@@ -441,9 +449,15 @@
         <v>대표자</v>
       </c>
       <c r="E2" t="str">
+        <v/>
+      </c>
+      <c r="F2" t="str">
+        <v/>
+      </c>
+      <c r="G2" t="str">
         <v>02-555-1234</v>
       </c>
-      <c r="F2" t="str">
+      <c r="H2" t="str">
         <v>경기도 부천시 송내대로265번길 59</v>
       </c>
     </row>
@@ -461,15 +475,21 @@
         <v>대표자</v>
       </c>
       <c r="E3" t="str">
+        <v/>
+      </c>
+      <c r="F3" t="str">
+        <v/>
+      </c>
+      <c r="G3" t="str">
         <v>02-555-1234</v>
       </c>
-      <c r="F3" t="str">
+      <c r="H3" t="str">
         <v>경기도 부천시 송내대로265번길 59</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:H3"/>
   </ignoredErrors>
 </worksheet>
 </file>